--- a/artfynd/A 35632-2025 artfynd.xlsx
+++ b/artfynd/A 35632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112276522</v>
+        <v>112276387</v>
       </c>
       <c r="B2" t="n">
-        <v>95754</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626419</v>
+        <v>626299</v>
       </c>
       <c r="R2" t="n">
-        <v>7023092</v>
+        <v>7022953</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112276417</v>
+        <v>112276403</v>
       </c>
       <c r="B3" t="n">
-        <v>94095</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626538</v>
+        <v>626238</v>
       </c>
       <c r="R3" t="n">
-        <v>7022874</v>
+        <v>7023216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112276402</v>
+        <v>112276400</v>
       </c>
       <c r="B4" t="n">
-        <v>56878</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>1968</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626238</v>
+        <v>626173</v>
       </c>
       <c r="R4" t="n">
-        <v>7023216</v>
+        <v>7023269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112276416</v>
+        <v>112276417</v>
       </c>
       <c r="B5" t="n">
-        <v>77441</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626468</v>
+        <v>626538</v>
       </c>
       <c r="R5" t="n">
-        <v>7022901</v>
+        <v>7022874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112276500</v>
+        <v>112276510</v>
       </c>
       <c r="B6" t="n">
-        <v>77441</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626111</v>
+        <v>626178</v>
       </c>
       <c r="R6" t="n">
-        <v>7023512</v>
+        <v>7023294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112276403</v>
+        <v>112276416</v>
       </c>
       <c r="B7" t="n">
-        <v>88678</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626238</v>
+        <v>626468</v>
       </c>
       <c r="R7" t="n">
-        <v>7023216</v>
+        <v>7022901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112276415</v>
+        <v>112276500</v>
       </c>
       <c r="B8" t="n">
-        <v>90851</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4363</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626468</v>
+        <v>626111</v>
       </c>
       <c r="R8" t="n">
-        <v>7022901</v>
+        <v>7023511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,6 +1351,200 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112276402</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundsbron, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626238</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7023216</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112276522</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sundsbron, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626419</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7023092</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35632-2025 artfynd.xlsx
+++ b/artfynd/A 35632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276387</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276417</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276510</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276416</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276402</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276522</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>